--- a/data/trans_dic/MCS12_SP_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,83</t>
+          <t>11,78; 16,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 22,95</t>
+          <t>17,36; 23,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,05; 21,33</t>
+          <t>15,21; 21,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 23,42</t>
+          <t>17,51; 23,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,68; 23,46</t>
+          <t>17,54; 23,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,56; 38,21</t>
+          <t>31,23; 38,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 30,55</t>
+          <t>24,4; 31,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 27,61</t>
+          <t>22,66; 27,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 19,46</t>
+          <t>15,28; 19,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,6; 29,59</t>
+          <t>24,81; 29,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,67; 25,23</t>
+          <t>20,72; 25,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,82; 24,81</t>
+          <t>20,87; 25,07</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 22,13</t>
+          <t>16,85; 22,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,3; 26,02</t>
+          <t>20,19; 25,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 18,8</t>
+          <t>14,27; 18,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 18,87</t>
+          <t>7,3; 18,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,97; 32,71</t>
+          <t>26,64; 32,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,73; 34,61</t>
+          <t>28,5; 34,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,92; 27,66</t>
+          <t>22,17; 27,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,37; 30,51</t>
+          <t>25,52; 30,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,58; 26,68</t>
+          <t>22,49; 26,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,45; 29,34</t>
+          <t>25,15; 29,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 22,42</t>
+          <t>18,94; 22,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,19; 23,53</t>
+          <t>13,01; 23,85</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 20,67</t>
+          <t>14,52; 20,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 23,59</t>
+          <t>17,44; 23,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,75</t>
+          <t>16,17; 21,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 25,35</t>
+          <t>18,46; 25,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,81; 29,42</t>
+          <t>22,76; 29,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,73; 34,77</t>
+          <t>27,14; 34,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,54; 30,2</t>
+          <t>23,47; 30,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,1; 68,18</t>
+          <t>24,09; 69,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,51; 23,93</t>
+          <t>19,6; 24,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,22; 27,97</t>
+          <t>23,5; 28,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 24,74</t>
+          <t>20,49; 25,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 56,35</t>
+          <t>22,69; 56,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,87</t>
+          <t>19,31; 24,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,82; 27,88</t>
+          <t>21,96; 28,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 24,9</t>
+          <t>19,85; 25,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,25; 22,5</t>
+          <t>17,15; 22,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,07; 30,89</t>
+          <t>25,35; 30,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,86; 36,81</t>
+          <t>31,0; 37,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,69; 31,52</t>
+          <t>25,82; 31,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,84; 30,76</t>
+          <t>21,44; 30,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,29; 27,02</t>
+          <t>23,37; 27,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 31,68</t>
+          <t>27,73; 31,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,62; 27,66</t>
+          <t>23,54; 27,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,89; 26,1</t>
+          <t>21,35; 26,14</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,32; 20,03</t>
+          <t>17,4; 20,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 23,76</t>
+          <t>20,79; 23,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,49; 20,2</t>
+          <t>17,6; 20,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,1; 20,31</t>
+          <t>14,57; 20,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,9; 28,14</t>
+          <t>25,04; 28,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,08; 34,52</t>
+          <t>30,98; 34,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,34; 28,3</t>
+          <t>25,33; 28,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,16; 43,29</t>
+          <t>26,19; 43,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,73</t>
+          <t>21,74; 23,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 28,57</t>
+          <t>26,49; 28,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,91; 23,92</t>
+          <t>21,93; 23,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,89; 32,04</t>
+          <t>21,81; 32,8</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80886; 116774</t>
+          <t>81721; 117367</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>120898; 161462</t>
+          <t>122107; 163876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101565; 143951</t>
+          <t>102638; 144688</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109777; 147604</t>
+          <t>110349; 150379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>121710; 161472</t>
+          <t>120733; 160883</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>213046; 266331</t>
+          <t>217698; 268319</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>161938; 205559</t>
+          <t>164200; 208741</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>151802; 184939</t>
+          <t>151758; 185270</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>212395; 269001</t>
+          <t>211225; 266665</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>344530; 414457</t>
+          <t>347490; 415488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>278600; 340000</t>
+          <t>279246; 339219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>270649; 322589</t>
+          <t>271349; 325875</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>161313; 212824</t>
+          <t>162044; 214870</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206677; 264854</t>
+          <t>205571; 262282</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144924; 192213</t>
+          <t>145941; 193481</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87717; 224176</t>
+          <t>86742; 223149</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>261193; 316764</t>
+          <t>257975; 316627</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>296586; 357198</t>
+          <t>294166; 360001</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>228598; 288512</t>
+          <t>231262; 288698</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>241704; 290744</t>
+          <t>243212; 289148</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>435805; 514991</t>
+          <t>434096; 514339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>521803; 601437</t>
+          <t>515618; 600736</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>389270; 463088</t>
+          <t>391101; 465286</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>282356; 503763</t>
+          <t>278593; 510583</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98213; 140244</t>
+          <t>98505; 140617</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>131898; 178720</t>
+          <t>132144; 177530</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119533; 165223</t>
+          <t>122814; 163750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128735; 178063</t>
+          <t>129644; 178209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>156002; 201186</t>
+          <t>155675; 199594</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>215482; 270213</t>
+          <t>210912; 267218</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>184753; 237107</t>
+          <t>184232; 235635</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>224558; 635205</t>
+          <t>224402; 647226</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>265770; 325976</t>
+          <t>267051; 328531</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>356324; 429261</t>
+          <t>360614; 434655</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>315543; 382078</t>
+          <t>316456; 387062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>371187; 920798</t>
+          <t>370684; 925739</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>184794; 234299</t>
+          <t>181942; 230856</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>206783; 264183</t>
+          <t>208098; 265760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>180899; 233408</t>
+          <t>186093; 235833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>159166; 207619</t>
+          <t>158321; 206866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>260388; 320810</t>
+          <t>263242; 321584</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>324645; 387158</t>
+          <t>326112; 390151</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>268186; 329046</t>
+          <t>269519; 329475</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>237917; 335094</t>
+          <t>233498; 335663</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>461419; 535194</t>
+          <t>462869; 537984</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>551210; 633461</t>
+          <t>554524; 639241</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>468060; 548073</t>
+          <t>466491; 546137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>420322; 525171</t>
+          <t>429609; 526034</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>567515; 656212</t>
+          <t>570263; 662516</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>713821; 814262</t>
+          <t>712305; 815399</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>593816; 685543</t>
+          <t>597445; 688115</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>485466; 699541</t>
+          <t>501790; 702537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>841377; 950929</t>
+          <t>846053; 947894</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1105945; 1228193</t>
+          <t>1102324; 1216963</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>898089; 1003188</t>
+          <t>897801; 1007196</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>953102; 1577346</t>
+          <t>954129; 1594929</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1444252; 1579259</t>
+          <t>1446647; 1569483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1847857; 1995433</t>
+          <t>1850649; 2004043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1519999; 1660006</t>
+          <t>1521629; 1663316</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1551484; 2271052</t>
+          <t>1545530; 2324808</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R3-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,78; 16,91</t>
+          <t>11,56; 16,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 23,3</t>
+          <t>17,04; 23,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 21,44</t>
+          <t>15,44; 21,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,51; 23,86</t>
+          <t>17,79; 24,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 23,37</t>
+          <t>17,43; 23,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,23; 38,49</t>
+          <t>30,62; 38,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,4; 31,02</t>
+          <t>24,07; 31,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 27,66</t>
+          <t>22,5; 27,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 19,29</t>
+          <t>15,45; 19,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,81; 29,67</t>
+          <t>24,59; 29,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,72; 25,17</t>
+          <t>20,53; 25,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,87; 25,07</t>
+          <t>20,88; 24,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,34</t>
+          <t>17,16; 22,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,77</t>
+          <t>20,14; 25,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,27; 18,92</t>
+          <t>13,84; 18,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 18,78</t>
+          <t>15,22; 20,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 32,7</t>
+          <t>26,71; 32,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,5; 34,88</t>
+          <t>28,78; 34,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,17; 27,68</t>
+          <t>22,23; 27,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,52; 30,35</t>
+          <t>25,78; 30,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,49; 26,65</t>
+          <t>22,51; 26,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,15; 29,3</t>
+          <t>25,22; 29,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 22,53</t>
+          <t>18,89; 22,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,01; 23,85</t>
+          <t>21,21; 24,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 20,72</t>
+          <t>14,58; 20,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 23,43</t>
+          <t>17,22; 23,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 21,56</t>
+          <t>16,09; 22,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,46; 25,37</t>
+          <t>17,86; 24,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,76; 29,19</t>
+          <t>22,86; 29,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,14; 34,38</t>
+          <t>27,43; 34,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,47; 30,02</t>
+          <t>23,36; 29,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,09; 69,47</t>
+          <t>24,46; 30,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,6; 24,12</t>
+          <t>19,66; 24,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,5; 28,32</t>
+          <t>23,43; 28,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,49; 25,06</t>
+          <t>20,69; 24,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,69; 56,66</t>
+          <t>21,9; 26,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 24,5</t>
+          <t>19,3; 24,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,96; 28,04</t>
+          <t>22,09; 27,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 25,15</t>
+          <t>19,75; 25,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,15; 22,41</t>
+          <t>17,97; 22,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,35; 30,96</t>
+          <t>25,33; 30,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,0; 37,09</t>
+          <t>31,02; 36,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,82; 31,57</t>
+          <t>25,72; 31,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,44; 30,82</t>
+          <t>27,51; 32,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 27,16</t>
+          <t>23,15; 27,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,73; 31,97</t>
+          <t>27,71; 31,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,54; 27,56</t>
+          <t>23,62; 27,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,35; 26,14</t>
+          <t>23,45; 27,05</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,4; 20,22</t>
+          <t>17,28; 19,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,79; 23,79</t>
+          <t>20,95; 23,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,6; 20,27</t>
+          <t>17,61; 20,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,57; 20,4</t>
+          <t>18,1; 21,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,04; 28,05</t>
+          <t>25,04; 27,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,98; 34,2</t>
+          <t>31,04; 34,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,33; 28,42</t>
+          <t>25,3; 28,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,19; 43,77</t>
+          <t>26,5; 28,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,58</t>
+          <t>21,66; 23,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,49; 28,69</t>
+          <t>26,52; 28,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,93; 23,97</t>
+          <t>21,93; 24,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,81; 32,8</t>
+          <t>22,94; 24,79</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128401</t>
+          <t>140598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>168207</t>
+          <t>182088</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>296608</t>
+          <t>322686</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81721; 117367</t>
+          <t>80230; 115774</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122107; 163876</t>
+          <t>119905; 162867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102638; 144688</t>
+          <t>104214; 143510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110349; 150379</t>
+          <t>121852; 165682</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>120733; 160883</t>
+          <t>119959; 161597</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>217698; 268319</t>
+          <t>213421; 265532</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>164200; 208741</t>
+          <t>161947; 210018</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>151758; 185270</t>
+          <t>163597; 202379</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>211225; 266665</t>
+          <t>213572; 266499</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>347490; 415488</t>
+          <t>344332; 413324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>279246; 339219</t>
+          <t>276692; 338794</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>271349; 325875</t>
+          <t>294822; 350837</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170639</t>
+          <t>182534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>266250</t>
+          <t>298579</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>436889</t>
+          <t>481113</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>162044; 214870</t>
+          <t>165084; 214366</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>205571; 262282</t>
+          <t>205031; 262121</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>145941; 193481</t>
+          <t>141534; 190881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86742; 223149</t>
+          <t>158905; 211031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>257975; 316627</t>
+          <t>258657; 316525</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>294166; 360001</t>
+          <t>297078; 359442</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>231262; 288698</t>
+          <t>231823; 287443</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>243212; 289148</t>
+          <t>274544; 323116</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>434096; 514339</t>
+          <t>434577; 509569</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515618; 600736</t>
+          <t>517057; 603952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>391101; 465286</t>
+          <t>390243; 465006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>278593; 510583</t>
+          <t>447205; 516631</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151966</t>
+          <t>167353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>389098</t>
+          <t>220550</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>541063</t>
+          <t>387903</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98505; 140617</t>
+          <t>98917; 139561</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>132144; 177530</t>
+          <t>130459; 179835</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122814; 163750</t>
+          <t>122226; 167195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129644; 178209</t>
+          <t>142922; 193238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>155675; 199594</t>
+          <t>156309; 202198</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>210912; 267218</t>
+          <t>213147; 265729</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>184232; 235635</t>
+          <t>183383; 233081</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>224402; 647226</t>
+          <t>198244; 243301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>267051; 328531</t>
+          <t>267801; 333227</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>360614; 434655</t>
+          <t>359614; 430909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>316456; 387062</t>
+          <t>319628; 384847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>370684; 925739</t>
+          <t>352740; 423766</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>181237</t>
+          <t>200526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>302668</t>
+          <t>330601</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>483905</t>
+          <t>531127</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>181942; 230856</t>
+          <t>181851; 232865</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>208098; 265760</t>
+          <t>209392; 261441</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>186093; 235833</t>
+          <t>185133; 236637</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>158321; 206866</t>
+          <t>177246; 224992</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>263242; 321584</t>
+          <t>263091; 319190</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>326112; 390151</t>
+          <t>326280; 386795</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>269519; 329475</t>
+          <t>268487; 325196</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>233498; 335663</t>
+          <t>306168; 359170</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>462869; 537984</t>
+          <t>458623; 538923</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>554524; 639241</t>
+          <t>554036; 634917</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>466491; 546137</t>
+          <t>467984; 545059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>429609; 526034</t>
+          <t>492231; 567834</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>632243</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1126222</t>
+          <t>1031818</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1758466</t>
+          <t>1722829</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>570263; 662516</t>
+          <t>566182; 653942</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>712305; 815399</t>
+          <t>718045; 817517</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>597445; 688115</t>
+          <t>597700; 686474</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>501790; 702537</t>
+          <t>636369; 741552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>846053; 947894</t>
+          <t>846234; 944763</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1102324; 1216963</t>
+          <t>1104449; 1223517</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>897801; 1007196</t>
+          <t>896862; 1007054</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>954129; 1594929</t>
+          <t>984640; 1076591</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1446647; 1569483</t>
+          <t>1441934; 1573020</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1850649; 2004043</t>
+          <t>1852183; 2000238</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1521629; 1663316</t>
+          <t>1521531; 1665479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1545530; 2324808</t>
+          <t>1658876; 1792341</t>
         </is>
       </c>
     </row>
